--- a/志愿填报表_v1.6_2026江苏专科_396分.xlsx
+++ b/志愿填报表_v1.6_2026江苏专科_396分.xlsx
@@ -589,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1858,14 +1858,124 @@
       <c r="J29" s="5" t="inlineStr"/>
       <c r="K29" s="5" t="inlineStr"/>
     </row>
+    <row r="30" outlineLevel="1" ht="58" customHeight="1">
+      <c r="A30" s="5">
+        <v>26</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>候补</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>江苏护理05</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>护理、中医、药学、检验、影像、康复等；另含智能医疗装备</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>2024为429分；2025首次投档低位</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>后置候补；护理计划244人，但组线不等于护理专业线</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>填6个可接受专业，不服从调剂</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>未核对</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>护理→中医学→医学检验技术→医学影像技术→口腔医学技术→康复治疗技术</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>智能医疗装备不接受；固定第26位</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" outlineLevel="1" ht="58" customHeight="1">
+      <c r="A31" s="5">
+        <v>27</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>候补</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>扬州职业大学08</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>护理、检验、药学、中药、宠物医疗、财会等；另含电子通信、建筑、道桥、测绘</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>2025为423分；护理仅15人</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>后置候补；大型混合组，不承担稳保任务</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>填6个可接受专业，不服从调剂</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>未核对</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>护理→医学检验技术→药学→中药学→宠物医疗技术→大数据与会计</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>六专业须本人复核；固定第27位</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:K29"/>
+  <autoFilter ref="A4:K31"/>
   <mergeCells count="3">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A3:K3"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H29">
+  <conditionalFormatting sqref="H5:H31">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$H5="拟填"</formula>
     </cfRule>
@@ -1873,16 +1983,16 @@
       <formula>$H5="不填"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I29">
+  <conditionalFormatting sqref="I5:I31">
     <cfRule type="expression" priority="3" dxfId="0">
       <formula>$I5="已核对"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="H5:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H5:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"待定,拟填,不填"</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="I5:I31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"未核对,已核对"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2227,7 +2337,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>常州幼师02、无锡师范03、南京旅游06、宿迁幼师02填满6个可接受专业，并选择不服从调剂。</t>
+          <t>常州幼师02、无锡师范03、南京旅游06、宿迁幼师02、江苏护理05、扬州职业大学08填满6个可接受专业，并选择不服从调剂。</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -2395,7 +2505,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>考生本人逐项确认25组的“是否填报”和组内专业顺序。</t>
+          <t>考生本人逐项确认27组的“是否填报”和组内专业顺序。</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -2504,7 +2614,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>V1.6；2026年7月26日生成Excel填报版</t>
+          <t>V1.6；2026年7月26日生成Excel填报版；7月27日增补2个后置候补组</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -2640,7 +2750,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>冲14组、稳6组、保5组，共25组</t>
+          <t>冲14组、稳6组、保5组、后置候补2组，共27组</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
